--- a/public/templates/warehouse_import_template.xlsx
+++ b/public/templates/warehouse_import_template.xlsx
@@ -9,7 +9,9 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="warehouse_import" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'warehouse_import'!$A$1:$G$4</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -425,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -474,11 +476,6 @@
           <t>reorder_point</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>unit_price_estimate</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -512,9 +509,6 @@
       <c r="G2" t="n">
         <v>2</v>
       </c>
-      <c r="H2" t="n">
-        <v>740000000</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -548,9 +542,6 @@
       <c r="G3" t="n">
         <v>3</v>
       </c>
-      <c r="H3" t="n">
-        <v>110000000</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -584,11 +575,9 @@
       <c r="G4" t="n">
         <v>20</v>
       </c>
-      <c r="H4" t="n">
-        <v>50000</v>
-      </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:G4"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>